--- a/www/flightdata/xlsx/eoss-346.xlsx
+++ b/www/flightdata/xlsx/eoss-346.xlsx
@@ -3075,7 +3075,7 @@
         <v>29330.6</v>
       </c>
       <c r="I2">
-        <v>564</v>
+        <v>376</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
